--- a/src/dataset_comparison_scripts/statistical_analysis/prerana_analysis/in_house_live_validation_three_way_split_clusters.xlsx
+++ b/src/dataset_comparison_scripts/statistical_analysis/prerana_analysis/in_house_live_validation_three_way_split_clusters.xlsx
@@ -1876,7 +1876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9959,156 +9959,174 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>george conway urges trump to resign over aborted iran strike</t>
+        </is>
+      </c>
+      <c r="B154" s="7">
+        <v>3</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>majority_accept</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="E154" s="3">
+        <v>2</v>
+      </c>
+      <c r="F154" s="4">
+        <v>1</v>
+      </c>
+      <c r="G154" s="7">
+        <v>3</v>
+      </c>
+      <c r="H154" s="7">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>bandwagon</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>persuasive propaganda</t>
+        </is>
+      </c>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>whose judgment no serious, intelligent person trusts</t>
+        </is>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>Aarush</t>
+        </is>
+      </c>
+      <c r="M154" s="7">
+        <v>1</v>
+      </c>
+      <c r="N154" s="7" t="inlineStr">
+        <is>
+          <t>Aarush</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>whose judgment no serious, intelligent person trusts</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B155" s="7">
         <v>0.0</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D154" s="8">
+      <c r="D155" s="8">
         <v>46054.0</v>
       </c>
-      <c r="E154" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F154" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G154" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H154" s="7">
+      <c r="E155" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F155" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G155" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H155" s="7">
         <v>0.666666666666666</v>
       </c>
-      <c r="I154" s="2" t="s">
+      <c r="I155" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J154" s="2" t="s">
+      <c r="J155" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K154" s="7" t="s">
+      <c r="K155" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L154" s="7" t="s">
+      <c r="L155" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="M154" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N154" s="7" t="s">
+      <c r="M155" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N155" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="O154" s="7" t="s">
+      <c r="O155" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="10" t="s">
+    <row r="156">
+      <c r="A156" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B156" s="10">
         <v>0.0</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C156" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D156" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E155" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F155" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G155" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H155" s="10">
+      <c r="E156" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F156" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G156" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H156" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I155" s="10" t="s">
+      <c r="I156" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J155" s="10" t="s">
+      <c r="J156" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K155" s="10" t="s">
+      <c r="K156" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="L155" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M155" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N155" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O155" s="10" t="s">
+      <c r="L156" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M156" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N156" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O156" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="P155" s="12"/>
-      <c r="Q155" s="12"/>
-      <c r="R155" s="12"/>
-      <c r="S155" s="12"/>
-      <c r="T155" s="12"/>
-      <c r="U155" s="12"/>
-      <c r="V155" s="12"/>
-      <c r="W155" s="12"/>
-      <c r="X155" s="12"/>
-      <c r="Y155" s="12"/>
-      <c r="Z155" s="12"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B156" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D156" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E156" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F156" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G156" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H156" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J156" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K156" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L156" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M156" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N156" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O156" s="7" t="s">
-        <v>199</v>
-      </c>
+      <c r="P156" s="12"/>
+      <c r="Q156" s="12"/>
+      <c r="R156" s="12"/>
+      <c r="S156" s="12"/>
+      <c r="T156" s="12"/>
+      <c r="U156" s="12"/>
+      <c r="V156" s="12"/>
+      <c r="W156" s="12"/>
+      <c r="X156" s="12"/>
+      <c r="Y156" s="12"/>
+      <c r="Z156" s="12"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="s">
@@ -10142,78 +10160,67 @@
         <v>18</v>
       </c>
       <c r="K157" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="L157" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M157" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N157" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O157" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B158" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D158" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E158" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F158" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G158" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H158" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="L157" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M157" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N157" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O157" s="7" t="s">
+      <c r="L158" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M158" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N158" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O158" s="7" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B158" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D158" s="11">
-        <v>46024.0</v>
-      </c>
-      <c r="E158" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F158" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G158" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H158" s="10">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="I158" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J158" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K158" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="L158" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M158" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N158" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O158" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="P158" s="12"/>
-      <c r="Q158" s="12"/>
-      <c r="R158" s="12"/>
-      <c r="S158" s="12"/>
-      <c r="T158" s="12"/>
-      <c r="U158" s="12"/>
-      <c r="V158" s="12"/>
-      <c r="W158" s="12"/>
-      <c r="X158" s="12"/>
-      <c r="Y158" s="12"/>
-      <c r="Z158" s="12"/>
     </row>
     <row r="159">
       <c r="A159" s="10" t="s">
@@ -10247,7 +10254,7 @@
         <v>25</v>
       </c>
       <c r="K159" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L159" s="10" t="s">
         <v>30</v>
@@ -10259,7 +10266,7 @@
         <v>30</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P159" s="12"/>
       <c r="Q159" s="12"/>
@@ -10274,51 +10281,62 @@
       <c r="Z159" s="12"/>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="10">
         <v>0.0</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D160" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E160" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F160" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G160" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H160" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K160" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="L160" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M160" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N160" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O160" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="C160" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160" s="11">
+        <v>46024.0</v>
+      </c>
+      <c r="E160" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F160" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G160" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H160" s="10">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K160" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="L160" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M160" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N160" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O160" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P160" s="12"/>
+      <c r="Q160" s="12"/>
+      <c r="R160" s="12"/>
+      <c r="S160" s="12"/>
+      <c r="T160" s="12"/>
+      <c r="U160" s="12"/>
+      <c r="V160" s="12"/>
+      <c r="W160" s="12"/>
+      <c r="X160" s="12"/>
+      <c r="Y160" s="12"/>
+      <c r="Z160" s="12"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="s">
@@ -10328,43 +10346,43 @@
         <v>0.0</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D161" s="8">
-        <v>46024.0</v>
+        <v>46054.0</v>
       </c>
       <c r="E161" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F161" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" s="7">
         <v>3.0</v>
       </c>
       <c r="H161" s="7">
-        <v>0.333333333333333</v>
+        <v>0.666666666666666</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M161" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N161" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>42</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162">
@@ -10372,46 +10390,46 @@
         <v>201</v>
       </c>
       <c r="B162" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D162" s="8">
-        <v>46054.0</v>
+        <v>46024.0</v>
       </c>
       <c r="E162" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F162" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G162" s="7">
         <v>3.0</v>
       </c>
       <c r="H162" s="7">
-        <v>0.666666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M162" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N162" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="163">
@@ -10422,359 +10440,359 @@
         <v>1.0</v>
       </c>
       <c r="C163" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D163" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E163" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F163" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G163" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H163" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L163" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M163" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N163" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O163" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B164" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D164" s="8">
         <v>46024.0</v>
       </c>
-      <c r="E163" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F163" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G163" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H163" s="7">
+      <c r="E164" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F164" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G164" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H164" s="7">
         <v>0.333333333333333</v>
       </c>
-      <c r="I163" s="2" t="s">
+      <c r="I164" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J163" s="2" t="s">
+      <c r="J164" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K163" s="7" t="s">
+      <c r="K164" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L163" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M163" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="N163" s="7" t="s">
+      <c r="L164" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M164" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N164" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="O163" s="7" t="s">
+      <c r="O164" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="10" t="s">
+    <row r="165">
+      <c r="A165" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B164" s="10">
+      <c r="B165" s="10">
         <v>0.0</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C165" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D164" s="11">
+      <c r="D165" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E164" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F164" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G164" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H164" s="10">
+      <c r="E165" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F165" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G165" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H165" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I164" s="10" t="s">
+      <c r="I165" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J164" s="10" t="s">
+      <c r="J165" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K164" s="10" t="s">
+      <c r="K165" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="L164" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M164" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N164" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O164" s="10" t="s">
+      <c r="L165" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M165" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N165" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O165" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="P164" s="12"/>
-      <c r="Q164" s="12"/>
-      <c r="R164" s="12"/>
-      <c r="S164" s="12"/>
-      <c r="T164" s="12"/>
-      <c r="U164" s="12"/>
-      <c r="V164" s="12"/>
-      <c r="W164" s="12"/>
-      <c r="X164" s="12"/>
-      <c r="Y164" s="12"/>
-      <c r="Z164" s="12"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="7" t="s">
+      <c r="P165" s="12"/>
+      <c r="Q165" s="12"/>
+      <c r="R165" s="12"/>
+      <c r="S165" s="12"/>
+      <c r="T165" s="12"/>
+      <c r="U165" s="12"/>
+      <c r="V165" s="12"/>
+      <c r="W165" s="12"/>
+      <c r="X165" s="12"/>
+      <c r="Y165" s="12"/>
+      <c r="Z165" s="12"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B166" s="7">
         <v>0.0</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D165" s="8">
+      <c r="D166" s="8">
         <v>46054.0</v>
       </c>
-      <c r="E165" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F165" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G165" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H165" s="7">
+      <c r="E166" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F166" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G166" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H166" s="7">
         <v>0.666666666666666</v>
       </c>
-      <c r="I165" s="2" t="s">
+      <c r="I166" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J165" s="2" t="s">
+      <c r="J166" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K165" s="7" t="s">
+      <c r="K166" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="L165" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M165" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N165" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O165" s="7" t="s">
+      <c r="L166" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M166" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N166" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O166" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="10" t="s">
+    <row r="167">
+      <c r="A167" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B167" s="10">
         <v>0.0</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C167" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D166" s="11">
+      <c r="D167" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E166" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F166" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G166" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H166" s="10">
+      <c r="E167" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F167" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G167" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H167" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I166" s="10" t="s">
+      <c r="I167" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J166" s="10" t="s">
+      <c r="J167" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K166" s="10" t="s">
+      <c r="K167" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="L166" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M166" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N166" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O166" s="10" t="s">
+      <c r="L167" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M167" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N167" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O167" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="P166" s="12"/>
-      <c r="Q166" s="12"/>
-      <c r="R166" s="12"/>
-      <c r="S166" s="12"/>
-      <c r="T166" s="12"/>
-      <c r="U166" s="12"/>
-      <c r="V166" s="12"/>
-      <c r="W166" s="12"/>
-      <c r="X166" s="12"/>
-      <c r="Y166" s="12"/>
-      <c r="Z166" s="12"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="s">
+      <c r="P167" s="12"/>
+      <c r="Q167" s="12"/>
+      <c r="R167" s="12"/>
+      <c r="S167" s="12"/>
+      <c r="T167" s="12"/>
+      <c r="U167" s="12"/>
+      <c r="V167" s="12"/>
+      <c r="W167" s="12"/>
+      <c r="X167" s="12"/>
+      <c r="Y167" s="12"/>
+      <c r="Z167" s="12"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B168" s="7">
         <v>0.0</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C168" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D167" s="8">
+      <c r="D168" s="8">
         <v>46024.0</v>
       </c>
-      <c r="E167" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F167" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G167" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H167" s="7">
+      <c r="E168" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F168" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G168" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H168" s="7">
         <v>0.333333333333333</v>
       </c>
-      <c r="I167" s="2" t="s">
+      <c r="I168" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J167" s="2" t="s">
+      <c r="J168" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K167" s="7" t="s">
+      <c r="K168" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L167" s="7" t="s">
+      <c r="L168" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M167" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="N167" s="7" t="s">
+      <c r="M168" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N168" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O167" s="7" t="s">
+      <c r="O168" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="10" t="s">
+    <row r="169">
+      <c r="A169" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B168" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C168" s="10" t="s">
+      <c r="B169" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C169" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D168" s="11">
+      <c r="D169" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E168" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F168" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G168" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H168" s="10">
+      <c r="E169" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F169" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G169" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H169" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I168" s="10" t="s">
+      <c r="I169" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J168" s="10" t="s">
+      <c r="J169" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K168" s="10" t="s">
+      <c r="K169" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="L168" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M168" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N168" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O168" s="10" t="s">
+      <c r="L169" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M169" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N169" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O169" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="P168" s="12"/>
-      <c r="Q168" s="12"/>
-      <c r="R168" s="12"/>
-      <c r="S168" s="12"/>
-      <c r="T168" s="12"/>
-      <c r="U168" s="12"/>
-      <c r="V168" s="12"/>
-      <c r="W168" s="12"/>
-      <c r="X168" s="12"/>
-      <c r="Y168" s="12"/>
-      <c r="Z168" s="12"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B169" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D169" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E169" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F169" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G169" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H169" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K169" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L169" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M169" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N169" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O169" s="7" t="s">
-        <v>211</v>
-      </c>
+      <c r="P169" s="12"/>
+      <c r="Q169" s="12"/>
+      <c r="R169" s="12"/>
+      <c r="S169" s="12"/>
+      <c r="T169" s="12"/>
+      <c r="U169" s="12"/>
+      <c r="V169" s="12"/>
+      <c r="W169" s="12"/>
+      <c r="X169" s="12"/>
+      <c r="Y169" s="12"/>
+      <c r="Z169" s="12"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="s">
@@ -10802,341 +10820,341 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I170" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="L170" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M170" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N170" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O170" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B171" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D171" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E171" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F171" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G171" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H171" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I171" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J170" s="2" t="s">
+      <c r="J171" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K170" s="7" t="s">
+      <c r="K171" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="L170" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M170" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N170" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O170" s="7" t="s">
+      <c r="L171" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M171" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N171" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O171" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="14" t="s">
+    <row r="172">
+      <c r="A172" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B171" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="C171" s="14" t="s">
+      <c r="B172" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="C172" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D171" s="15">
+      <c r="D172" s="15">
         <v>46024.0</v>
       </c>
-      <c r="E171" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="F171" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="G171" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="H171" s="14">
+      <c r="E172" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="F172" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="G172" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H172" s="14">
         <v>0.333333333333333</v>
       </c>
-      <c r="I171" s="14" t="s">
+      <c r="I172" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="J171" s="14" t="s">
+      <c r="J172" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K171" s="14" t="s">
+      <c r="K172" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="L171" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M171" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="N171" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O171" s="14" t="s">
+      <c r="L172" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M172" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N172" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O172" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="P171" s="16"/>
-      <c r="Q171" s="16"/>
-      <c r="R171" s="16"/>
-      <c r="S171" s="16"/>
-      <c r="T171" s="16"/>
-      <c r="U171" s="16"/>
-      <c r="V171" s="16"/>
-      <c r="W171" s="16"/>
-      <c r="X171" s="16"/>
-      <c r="Y171" s="16"/>
-      <c r="Z171" s="16"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="7" t="s">
+      <c r="P172" s="16"/>
+      <c r="Q172" s="16"/>
+      <c r="R172" s="16"/>
+      <c r="S172" s="16"/>
+      <c r="T172" s="16"/>
+      <c r="U172" s="16"/>
+      <c r="V172" s="16"/>
+      <c r="W172" s="16"/>
+      <c r="X172" s="16"/>
+      <c r="Y172" s="16"/>
+      <c r="Z172" s="16"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B172" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C172" s="2" t="s">
+      <c r="B173" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D172" s="8">
+      <c r="D173" s="8">
         <v>46054.0</v>
       </c>
-      <c r="E172" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F172" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G172" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H172" s="7">
+      <c r="E173" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F173" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G173" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H173" s="7">
         <v>0.666666666666666</v>
       </c>
-      <c r="I172" s="2" t="s">
+      <c r="I173" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J172" s="2" t="s">
+      <c r="J173" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K172" s="7" t="s">
+      <c r="K173" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="L172" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M172" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N172" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O172" s="7" t="s">
+      <c r="L173" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M173" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N173" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O173" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="10" t="s">
+    <row r="174">
+      <c r="A174" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B173" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="C173" s="10" t="s">
+      <c r="B174" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="C174" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D174" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E173" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F173" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G173" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H173" s="10">
+      <c r="E174" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F174" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G174" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H174" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I173" s="10" t="s">
+      <c r="I174" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J173" s="10" t="s">
+      <c r="J174" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K173" s="10" t="s">
+      <c r="K174" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="L173" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M173" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N173" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O173" s="10" t="s">
+      <c r="L174" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M174" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N174" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O174" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="P173" s="12"/>
-      <c r="Q173" s="12"/>
-      <c r="R173" s="12"/>
-      <c r="S173" s="12"/>
-      <c r="T173" s="12"/>
-      <c r="U173" s="12"/>
-      <c r="V173" s="12"/>
-      <c r="W173" s="12"/>
-      <c r="X173" s="12"/>
-      <c r="Y173" s="12"/>
-      <c r="Z173" s="12"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="7" t="s">
+      <c r="P174" s="12"/>
+      <c r="Q174" s="12"/>
+      <c r="R174" s="12"/>
+      <c r="S174" s="12"/>
+      <c r="T174" s="12"/>
+      <c r="U174" s="12"/>
+      <c r="V174" s="12"/>
+      <c r="W174" s="12"/>
+      <c r="X174" s="12"/>
+      <c r="Y174" s="12"/>
+      <c r="Z174" s="12"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B174" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="C174" s="2" t="s">
+      <c r="B175" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D174" s="8">
+      <c r="D175" s="8">
         <v>46024.0</v>
       </c>
-      <c r="E174" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F174" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G174" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H174" s="7">
+      <c r="E175" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F175" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G175" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H175" s="7">
         <v>0.333333333333333</v>
       </c>
-      <c r="I174" s="2" t="s">
+      <c r="I175" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J174" s="2" t="s">
+      <c r="J175" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K174" s="7" t="s">
+      <c r="K175" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L174" s="7" t="s">
+      <c r="L175" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M174" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="N174" s="7" t="s">
+      <c r="M175" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N175" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O174" s="7" t="s">
+      <c r="O175" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="10" t="s">
+    <row r="176">
+      <c r="A176" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B175" s="10">
+      <c r="B176" s="10">
         <v>0.0</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C176" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D175" s="11">
+      <c r="D176" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E175" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F175" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G175" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H175" s="10">
+      <c r="E176" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F176" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G176" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H176" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I175" s="10" t="s">
+      <c r="I176" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J175" s="10" t="s">
+      <c r="J176" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K175" s="10" t="s">
+      <c r="K176" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L175" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M175" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N175" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O175" s="10" t="s">
+      <c r="L176" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M176" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N176" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O176" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="P175" s="12"/>
-      <c r="Q175" s="12"/>
-      <c r="R175" s="12"/>
-      <c r="S175" s="12"/>
-      <c r="T175" s="12"/>
-      <c r="U175" s="12"/>
-      <c r="V175" s="12"/>
-      <c r="W175" s="12"/>
-      <c r="X175" s="12"/>
-      <c r="Y175" s="12"/>
-      <c r="Z175" s="12"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B176" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D176" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E176" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F176" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G176" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H176" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I176" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J176" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K176" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="L176" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M176" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N176" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O176" s="7" t="s">
-        <v>218</v>
-      </c>
+      <c r="P176" s="12"/>
+      <c r="Q176" s="12"/>
+      <c r="R176" s="12"/>
+      <c r="S176" s="12"/>
+      <c r="T176" s="12"/>
+      <c r="U176" s="12"/>
+      <c r="V176" s="12"/>
+      <c r="W176" s="12"/>
+      <c r="X176" s="12"/>
+      <c r="Y176" s="12"/>
+      <c r="Z176" s="12"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="s">
@@ -11164,131 +11182,131 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I177" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L177" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M177" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N177" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O177" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B178" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D178" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E178" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F178" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G178" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H178" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I178" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J177" s="2" t="s">
+      <c r="J178" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K177" s="7" t="s">
+      <c r="K178" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L177" s="7" t="s">
+      <c r="L178" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M177" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="N177" s="7" t="s">
+      <c r="M178" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N178" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O177" s="7" t="s">
+      <c r="O178" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="10" t="s">
+    <row r="179">
+      <c r="A179" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B179" s="10">
         <v>0.0</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C179" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D178" s="11">
+      <c r="D179" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E178" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F178" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G178" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H178" s="10">
+      <c r="E179" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F179" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G179" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H179" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I178" s="10" t="s">
+      <c r="I179" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J178" s="10" t="s">
+      <c r="J179" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K178" s="10" t="s">
+      <c r="K179" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="L178" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M178" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N178" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O178" s="10" t="s">
+      <c r="L179" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M179" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N179" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O179" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="P178" s="12"/>
-      <c r="Q178" s="12"/>
-      <c r="R178" s="12"/>
-      <c r="S178" s="12"/>
-      <c r="T178" s="12"/>
-      <c r="U178" s="12"/>
-      <c r="V178" s="12"/>
-      <c r="W178" s="12"/>
-      <c r="X178" s="12"/>
-      <c r="Y178" s="12"/>
-      <c r="Z178" s="12"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B179" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D179" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E179" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F179" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G179" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H179" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J179" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K179" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="L179" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M179" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N179" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O179" s="7" t="s">
-        <v>221</v>
-      </c>
+      <c r="P179" s="12"/>
+      <c r="Q179" s="12"/>
+      <c r="R179" s="12"/>
+      <c r="S179" s="12"/>
+      <c r="T179" s="12"/>
+      <c r="U179" s="12"/>
+      <c r="V179" s="12"/>
+      <c r="W179" s="12"/>
+      <c r="X179" s="12"/>
+      <c r="Y179" s="12"/>
+      <c r="Z179" s="12"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="s">
@@ -11316,84 +11334,73 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="L180" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M180" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N180" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O180" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B181" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D181" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E181" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F181" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G181" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H181" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L180" s="7" t="s">
+      <c r="L181" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M180" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N180" s="7" t="s">
+      <c r="M181" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N181" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O180" s="7" t="s">
+      <c r="O181" s="7" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="B181" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="C181" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D181" s="11">
-        <v>46024.0</v>
-      </c>
-      <c r="E181" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F181" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G181" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H181" s="10">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="I181" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J181" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K181" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="L181" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M181" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N181" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O181" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="P181" s="12"/>
-      <c r="Q181" s="12"/>
-      <c r="R181" s="12"/>
-      <c r="S181" s="12"/>
-      <c r="T181" s="12"/>
-      <c r="U181" s="12"/>
-      <c r="V181" s="12"/>
-      <c r="W181" s="12"/>
-      <c r="X181" s="12"/>
-      <c r="Y181" s="12"/>
-      <c r="Z181" s="12"/>
     </row>
     <row r="182">
       <c r="A182" s="10" t="s">
@@ -11421,25 +11428,25 @@
         <v>0.333333333333333</v>
       </c>
       <c r="I182" s="10" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J182" s="10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K182" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L182" s="10" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="M182" s="10">
         <v>1.0</v>
       </c>
       <c r="N182" s="10" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="O182" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P182" s="12"/>
       <c r="Q182" s="12"/>
@@ -11455,10 +11462,10 @@
     </row>
     <row r="183">
       <c r="A183" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B183" s="10">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>27</v>
@@ -11479,25 +11486,25 @@
         <v>0.333333333333333</v>
       </c>
       <c r="I183" s="10" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J183" s="10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K183" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L183" s="10" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="M183" s="10">
         <v>1.0</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P183" s="12"/>
       <c r="Q183" s="12"/>
@@ -11537,13 +11544,13 @@
         <v>0.333333333333333</v>
       </c>
       <c r="I184" s="10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J184" s="10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K184" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L184" s="10" t="s">
         <v>30</v>
@@ -11555,7 +11562,7 @@
         <v>30</v>
       </c>
       <c r="O184" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P184" s="12"/>
       <c r="Q184" s="12"/>
@@ -11601,7 +11608,7 @@
         <v>25</v>
       </c>
       <c r="K185" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L185" s="10" t="s">
         <v>30</v>
@@ -11613,7 +11620,7 @@
         <v>30</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P185" s="12"/>
       <c r="Q185" s="12"/>
@@ -11628,163 +11635,174 @@
       <c r="Z185" s="12"/>
     </row>
     <row r="186">
-      <c r="A186" s="7" t="s">
+      <c r="A186" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B186" s="7">
+      <c r="B186" s="10">
         <v>0.0</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D186" s="11">
+        <v>46024.0</v>
+      </c>
+      <c r="E186" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F186" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G186" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H186" s="10">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="I186" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J186" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K186" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="L186" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M186" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N186" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O186" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P186" s="12"/>
+      <c r="Q186" s="12"/>
+      <c r="R186" s="12"/>
+      <c r="S186" s="12"/>
+      <c r="T186" s="12"/>
+      <c r="U186" s="12"/>
+      <c r="V186" s="12"/>
+      <c r="W186" s="12"/>
+      <c r="X186" s="12"/>
+      <c r="Y186" s="12"/>
+      <c r="Z186" s="12"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B187" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D186" s="8">
+      <c r="D187" s="8">
         <v>46054.0</v>
       </c>
-      <c r="E186" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F186" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G186" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H186" s="7">
+      <c r="E187" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F187" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G187" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H187" s="7">
         <v>0.666666666666666</v>
       </c>
-      <c r="I186" s="2" t="s">
+      <c r="I187" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J186" s="2" t="s">
+      <c r="J187" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K186" s="7" t="s">
+      <c r="K187" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="L186" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M186" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N186" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O186" s="7" t="s">
+      <c r="L187" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M187" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N187" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O187" s="7" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="10" t="s">
+    <row r="188">
+      <c r="A188" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B187" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="C187" s="10" t="s">
+      <c r="B188" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="C188" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D188" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E187" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F187" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G187" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H187" s="10">
+      <c r="E188" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F188" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G188" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H188" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I187" s="10" t="s">
+      <c r="I188" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J187" s="10" t="s">
+      <c r="J188" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K187" s="10" t="s">
+      <c r="K188" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="L187" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M187" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N187" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O187" s="10" t="s">
+      <c r="L188" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M188" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N188" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O188" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="P187" s="12"/>
-      <c r="Q187" s="12"/>
-      <c r="R187" s="12"/>
-      <c r="S187" s="12"/>
-      <c r="T187" s="12"/>
-      <c r="U187" s="12"/>
-      <c r="V187" s="12"/>
-      <c r="W187" s="12"/>
-      <c r="X187" s="12"/>
-      <c r="Y187" s="12"/>
-      <c r="Z187" s="12"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B188" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D188" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E188" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F188" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G188" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H188" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I188" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J188" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K188" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="L188" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M188" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N188" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O188" s="7" t="s">
-        <v>231</v>
-      </c>
+      <c r="P188" s="12"/>
+      <c r="Q188" s="12"/>
+      <c r="R188" s="12"/>
+      <c r="S188" s="12"/>
+      <c r="T188" s="12"/>
+      <c r="U188" s="12"/>
+      <c r="V188" s="12"/>
+      <c r="W188" s="12"/>
+      <c r="X188" s="12"/>
+      <c r="Y188" s="12"/>
+      <c r="Z188" s="12"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="s">
         <v>225</v>
       </c>
       <c r="B189" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>16</v>
@@ -11811,85 +11829,74 @@
         <v>25</v>
       </c>
       <c r="K189" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L189" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M189" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N189" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O189" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B190" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D190" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E190" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F190" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G190" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H190" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K190" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="L189" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M189" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N189" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O189" s="7" t="s">
+      <c r="L190" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M190" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N190" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O190" s="7" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B190" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="C190" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D190" s="11">
-        <v>46024.0</v>
-      </c>
-      <c r="E190" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="F190" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G190" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="H190" s="10">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="I190" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J190" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K190" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="L190" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M190" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="N190" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O190" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="P190" s="12"/>
-      <c r="Q190" s="12"/>
-      <c r="R190" s="12"/>
-      <c r="S190" s="12"/>
-      <c r="T190" s="12"/>
-      <c r="U190" s="12"/>
-      <c r="V190" s="12"/>
-      <c r="W190" s="12"/>
-      <c r="X190" s="12"/>
-      <c r="Y190" s="12"/>
-      <c r="Z190" s="12"/>
     </row>
     <row r="191">
       <c r="A191" s="10" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B191" s="10">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C191" s="10" t="s">
         <v>27</v>
@@ -11916,7 +11923,7 @@
         <v>25</v>
       </c>
       <c r="K191" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L191" s="10" t="s">
         <v>30</v>
@@ -11928,7 +11935,7 @@
         <v>30</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P191" s="12"/>
       <c r="Q191" s="12"/>
@@ -11974,7 +11981,7 @@
         <v>25</v>
       </c>
       <c r="K192" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L192" s="10" t="s">
         <v>30</v>
@@ -11986,7 +11993,7 @@
         <v>30</v>
       </c>
       <c r="O192" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P192" s="12"/>
       <c r="Q192" s="12"/>
@@ -12001,58 +12008,109 @@
       <c r="Z192" s="12"/>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="s">
+      <c r="A193" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193" s="10">
         <v>0.0</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C193" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D193" s="8">
+      <c r="D193" s="11">
         <v>46024.0</v>
       </c>
-      <c r="E193" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F193" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G193" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H193" s="7">
+      <c r="E193" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F193" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="G193" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H193" s="10">
         <v>0.333333333333333</v>
       </c>
-      <c r="I193" s="2" t="s">
+      <c r="I193" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J193" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K193" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L193" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M193" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N193" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O193" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="P193" s="12"/>
+      <c r="Q193" s="12"/>
+      <c r="R193" s="12"/>
+      <c r="S193" s="12"/>
+      <c r="T193" s="12"/>
+      <c r="U193" s="12"/>
+      <c r="V193" s="12"/>
+      <c r="W193" s="12"/>
+      <c r="X193" s="12"/>
+      <c r="Y193" s="12"/>
+      <c r="Z193" s="12"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B194" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" s="8">
+        <v>46024.0</v>
+      </c>
+      <c r="E194" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F194" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G194" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H194" s="7">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="I194" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J193" s="2" t="s">
+      <c r="J194" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K193" s="7" t="s">
+      <c r="K194" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L193" s="7" t="s">
+      <c r="L194" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M193" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="N193" s="7" t="s">
+      <c r="M194" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N194" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O193" s="7" t="s">
+      <c r="O194" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="194">
-      <c r="C194" s="17"/>
-      <c r="E194" s="18"/>
-      <c r="F194" s="19"/>
-      <c r="I194" s="17"/>
-      <c r="J194" s="17"/>
     </row>
     <row r="195">
       <c r="C195" s="17"/>
@@ -17695,6 +17753,13 @@
       <c r="F1000" s="19"/>
       <c r="I1000" s="17"/>
       <c r="J1000" s="17"/>
+    </row>
+    <row r="1001">
+      <c r="C1001" s="17"/>
+      <c r="E1001" s="18"/>
+      <c r="F1001" s="19"/>
+      <c r="I1001" s="17"/>
+      <c r="J1001" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$Z$193"/>
@@ -17704,7 +17769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -21710,50 +21775,68 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="s">
-        <v>197</v>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>george conway urges trump to resign over aborted iran strike</t>
+        </is>
       </c>
       <c r="B86" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="8">
-        <v>46054.0</v>
+        <v>3</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>majority_accept</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
       </c>
       <c r="E86" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F86" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H86" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>57</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>bandwagon</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>persuasive propaganda</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>whose judgment no serious, intelligent person trusts</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>Aarush</t>
+        </is>
       </c>
       <c r="M86" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N86" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="O86" s="7" t="s">
-        <v>198</v>
+        <v>1</v>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>Aarush</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>whose judgment no serious, intelligent person trusts</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -21782,25 +21865,25 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="M87" s="7">
         <v>1.0</v>
       </c>
       <c r="N87" s="7" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88">
@@ -21835,7 +21918,7 @@
         <v>18</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>30</v>
@@ -21847,12 +21930,12 @@
         <v>30</v>
       </c>
       <c r="O88" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B89" s="7">
         <v>0.0</v>
@@ -21876,13 +21959,13 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>30</v>
@@ -21894,7 +21977,7 @@
         <v>30</v>
       </c>
       <c r="O89" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90">
@@ -21905,43 +21988,43 @@
         <v>0.0</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D90" s="8">
-        <v>46024.0</v>
+        <v>46054.0</v>
       </c>
       <c r="E90" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F90" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" s="7">
         <v>3.0</v>
       </c>
       <c r="H90" s="7">
-        <v>0.333333333333333</v>
+        <v>0.666666666666666</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M90" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N90" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O90" s="7" t="s">
-        <v>42</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91">
@@ -21949,46 +22032,46 @@
         <v>201</v>
       </c>
       <c r="B91" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D91" s="8">
-        <v>46054.0</v>
+        <v>46024.0</v>
       </c>
       <c r="E91" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F91" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" s="7">
         <v>3.0</v>
       </c>
       <c r="H91" s="7">
-        <v>0.666666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M91" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
@@ -21999,90 +22082,90 @@
         <v>1.0</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D92" s="8">
-        <v>46024.0</v>
+        <v>46054.0</v>
       </c>
       <c r="E92" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F92" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G92" s="7">
         <v>3.0</v>
       </c>
       <c r="H92" s="7">
-        <v>0.333333333333333</v>
+        <v>0.666666666666666</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>40</v>
+        <v>205</v>
       </c>
       <c r="L92" s="7" t="s">
         <v>30</v>
       </c>
       <c r="M92" s="7">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N92" s="7" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="O92" s="7" t="s">
-        <v>140</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B93" s="7">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D93" s="8">
-        <v>46054.0</v>
+        <v>46024.0</v>
       </c>
       <c r="E93" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F93" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" s="7">
         <v>3.0</v>
       </c>
       <c r="H93" s="7">
-        <v>0.666666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="L93" s="7" t="s">
         <v>30</v>
       </c>
       <c r="M93" s="7">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N93" s="7" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="O93" s="7" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94">
@@ -22093,43 +22176,43 @@
         <v>0.0</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D94" s="8">
-        <v>46024.0</v>
+        <v>46054.0</v>
       </c>
       <c r="E94" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F94" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G94" s="7">
         <v>3.0</v>
       </c>
       <c r="H94" s="7">
-        <v>0.333333333333333</v>
+        <v>0.666666666666666</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M94" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N94" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O94" s="7" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95">
@@ -22137,46 +22220,46 @@
         <v>206</v>
       </c>
       <c r="B95" s="7">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D95" s="8">
-        <v>46054.0</v>
+        <v>46024.0</v>
       </c>
       <c r="E95" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F95" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95" s="7">
         <v>3.0</v>
       </c>
       <c r="H95" s="7">
-        <v>0.666666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M95" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N95" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O95" s="7" t="s">
-        <v>211</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96">
@@ -22205,119 +22288,119 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M96" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N96" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O96" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B97" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E97" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H97" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I97" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="J97" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K96" s="7" t="s">
+      <c r="K97" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="L96" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M96" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N96" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O96" s="7" t="s">
+      <c r="L97" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M97" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N97" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O97" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="14" t="s">
+    <row r="98">
+      <c r="A98" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B97" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="C97" s="14" t="s">
+      <c r="B98" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="C98" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D97" s="15">
+      <c r="D98" s="15">
         <v>46024.0</v>
       </c>
-      <c r="E97" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="F97" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="G97" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="H97" s="14">
+      <c r="E98" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="F98" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="G98" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="H98" s="14">
         <v>0.333333333333333</v>
       </c>
-      <c r="I97" s="14" t="s">
+      <c r="I98" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="J97" s="14" t="s">
+      <c r="J98" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K97" s="14" t="s">
+      <c r="K98" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="L97" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M97" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="N97" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O97" s="14" t="s">
+      <c r="L98" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M98" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="N98" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O98" s="14" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B98" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" s="8">
-        <v>46054.0</v>
-      </c>
-      <c r="E98" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F98" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G98" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H98" s="7">
-        <v>0.666666666666666</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M98" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="N98" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O98" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="99">
@@ -22325,93 +22408,93 @@
         <v>206</v>
       </c>
       <c r="B99" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D99" s="8">
-        <v>46024.0</v>
+        <v>46054.0</v>
       </c>
       <c r="E99" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F99" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" s="7">
         <v>3.0</v>
       </c>
       <c r="H99" s="7">
-        <v>0.333333333333333</v>
+        <v>0.666666666666666</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M99" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N99" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B100" s="7">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D100" s="8">
-        <v>46054.0</v>
+        <v>46024.0</v>
       </c>
       <c r="E100" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F100" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" s="7">
         <v>3.0</v>
       </c>
       <c r="H100" s="7">
-        <v>0.666666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>218</v>
+        <v>40</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M100" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N100" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O100" s="7" t="s">
-        <v>218</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101">
@@ -22440,30 +22523,30 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M101" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N101" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>42</v>
+        <v>218</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B102" s="7">
         <v>1.0</v>
@@ -22487,25 +22570,25 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>221</v>
+        <v>40</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M102" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N102" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O102" s="7" t="s">
-        <v>221</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103">
@@ -22534,33 +22617,33 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M103" s="7">
         <v>1.0</v>
       </c>
       <c r="N103" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B104" s="7">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>16</v>
@@ -22581,25 +22664,25 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M104" s="7">
         <v>1.0</v>
       </c>
       <c r="N104" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O104" s="7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105">
@@ -22607,7 +22690,7 @@
         <v>225</v>
       </c>
       <c r="B105" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>16</v>
@@ -22628,13 +22711,13 @@
         <v>0.666666666666666</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L105" s="7" t="s">
         <v>30</v>
@@ -22646,7 +22729,7 @@
         <v>30</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106">
@@ -22654,7 +22737,7 @@
         <v>225</v>
       </c>
       <c r="B106" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>16</v>
@@ -22681,7 +22764,7 @@
         <v>25</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L106" s="7" t="s">
         <v>30</v>
@@ -22693,53 +22776,100 @@
         <v>30</v>
       </c>
       <c r="O106" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="8">
+        <v>46054.0</v>
+      </c>
+      <c r="E107" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G107" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H107" s="7">
+        <v>0.666666666666666</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M107" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N107" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B108" s="7">
         <v>0.0</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D108" s="8">
         <v>46024.0</v>
       </c>
-      <c r="E107" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F107" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G107" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="H107" s="7">
+      <c r="E108" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F108" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G108" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="H108" s="7">
         <v>0.333333333333333</v>
       </c>
-      <c r="I107" s="2" t="s">
+      <c r="I108" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="J108" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K107" s="7" t="s">
+      <c r="K108" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L107" s="7" t="s">
+      <c r="L108" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M107" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="N107" s="7" t="s">
+      <c r="M108" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N108" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O107" s="7" t="s">
+      <c r="O108" s="7" t="s">
         <v>42</v>
       </c>
     </row>
